--- a/02_DIA_inicio_2026_analisis_assets/rbd_9703_escuela-esperanza-joven_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9703_escuela-esperanza-joven_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C80DCF35-9B72-44EC-8B04-FFA2A08A2F8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55ABE560-8759-4AD7-9F3B-F05281FE52FE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F7EA77-B2ED-4897-9012-620F01672680}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71DD8A33-980F-4711-9FAC-7C51B0875E7E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5802B929-058A-4299-9787-9CC3DA05D681}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00D89403-CD04-4986-B025-522716FC1731}"/>
 </file>